--- a/skills/rv-park-autofill/RV_Park_Underwriting.xlsx
+++ b/skills/rv-park-autofill/RV_Park_Underwriting.xlsx
@@ -12,12 +12,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal Scorecard" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Underwriting" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normalization" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offer Structures" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income Detail" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actuals vs Pro Forma" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pro Forma &amp; Returns" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loan Sizing" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operator &amp; Capital" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offer Structures" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income Detail" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actuals vs Pro Forma" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pro Forma &amp; Returns" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loan Sizing" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -170,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -269,6 +270,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -712,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A63"/>
+  <dimension ref="A1:A64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="104" customWidth="1" min="1" max="1"/>
@@ -980,140 +984,147 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Offer Structures — Linda's 4-column engine: Seller / Conventional / Partial carry / Full carry, two-lien</t>
+          <t xml:space="preserve">  • Operator &amp; Capital — a hands-off hold: pay an operator, size the value-add capital, see TRUE cash-on-cash.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">      debt stack, blended rate, and the auto-solved Maximum Allowable Offer (MAO).</t>
+          <t xml:space="preserve">  • Offer Structures — Linda's 4-column engine: Seller / Conventional / Partial carry / Full carry, two-lien</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Income Detail — optional. Build income from your site mix (long-term + seasonal nightly).</t>
+          <t xml:space="preserve">      debt stack, blended rate, and the auto-solved Maximum Allowable Offer (MAO).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Actuals vs Pro Forma — seller's CURRENT numbers vs your stabilized plan, side by side.</t>
+          <t xml:space="preserve">  • Income Detail — optional. Build income from your site mix (long-term + seasonal nightly).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Pro Forma &amp; Returns — 10-year projection, sale reversion, IRR &amp; equity multiple.</t>
+          <t xml:space="preserve">  • Actuals vs Pro Forma — seller's CURRENT numbers vs your stabilized plan, side by side.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Sensitivity   — the Bad-Day Test: CoC &amp; DSCR vs price, interest rate, rent &amp; vacancy.</t>
+          <t xml:space="preserve">  • Pro Forma &amp; Returns — 10-year projection, sale reversion, IRR &amp; equity multiple.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  • Sensitivity   — the Bad-Day Test: CoC &amp; DSCR vs price, interest rate, rent &amp; vacancy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  • Loan Sizing   — max purchase price the NOI supports at your target DSCR / debt yield.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr"/>
-    </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>HOW TO USE IT</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>1. Normalization tab: enter the seller's reported expenses; read off your normalized NOI.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2. Underwriting tab: fill the yellow cells using those NORMALIZED numbers, not the seller's.</t>
+          <t>1. Normalization tab: enter the seller's reported expenses; read off your normalized NOI.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>3. Deal Scorecard: read the GOOD/OK/BAD ratings and the GO / CONDITIONAL / NO-GO verdict.</t>
+          <t>2. Underwriting tab: fill the yellow cells using those NORMALIZED numbers, not the seller's.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>3. Deal Scorecard: read the GOOD/OK/BAD ratings and the GO / CONDITIONAL / NO-GO verdict.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
           <t>4. Sensitivity: run the bad-day stress test. Deal Summary: the one-page headline.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr"/>
-    </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>RV-PARK / MHP WATCH-OUTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Nondisclosure states: sellers needn't volunteer problems (failing septic, AC, zoning). Dig.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Transient/nightly income is seasonal and far less stable than annual/monthly tenants.</t>
+          <t xml:space="preserve">  • Nondisclosure states: sellers needn't volunteer problems (failing septic, AC, zoning). Dig.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Utility metering — are sites individually metered, or is the owner eating utilities? (ratio bill-back).</t>
+          <t xml:space="preserve">  • Transient/nightly income is seasonal and far less stable than annual/monthly tenants.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Infrastructure age — septic/sewer, electric pedestals (30/50 amp), water lines = big CapEx.</t>
+          <t xml:space="preserve">  • Utility metering — are sites individually metered, or is the owner eating utilities? (ratio bill-back).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  • Infrastructure age — septic/sewer, electric pedestals (30/50 amp), water lines = big CapEx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  • Property taxes usually RESET on sale — don't trust the seller's current tax line.</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr"/>
-    </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>This is a screening tool, not investment advice. Verify every number and consult professionals.</t>
         </is>
@@ -1125,6 +1136,703 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>10-YEAR PRO FORMA &amp; RETURNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="50" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="L3" s="16" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Gross Potential Rent</t>
+        </is>
+      </c>
+      <c r="C5" s="28">
+        <f>Underwriting!B21*(1+Underwriting!B16)^0</f>
+        <v/>
+      </c>
+      <c r="D5" s="28">
+        <f>Underwriting!B21*(1+Underwriting!B16)^1</f>
+        <v/>
+      </c>
+      <c r="E5" s="28">
+        <f>Underwriting!B21*(1+Underwriting!B16)^2</f>
+        <v/>
+      </c>
+      <c r="F5" s="28">
+        <f>Underwriting!B21*(1+Underwriting!B16)^3</f>
+        <v/>
+      </c>
+      <c r="G5" s="28">
+        <f>Underwriting!B21*(1+Underwriting!B16)^4</f>
+        <v/>
+      </c>
+      <c r="H5" s="28">
+        <f>Underwriting!B21*(1+Underwriting!B16)^5</f>
+        <v/>
+      </c>
+      <c r="I5" s="28">
+        <f>Underwriting!B21*(1+Underwriting!B16)^6</f>
+        <v/>
+      </c>
+      <c r="J5" s="28">
+        <f>Underwriting!B21*(1+Underwriting!B16)^7</f>
+        <v/>
+      </c>
+      <c r="K5" s="28">
+        <f>Underwriting!B21*(1+Underwriting!B16)^8</f>
+        <v/>
+      </c>
+      <c r="L5" s="28">
+        <f>Underwriting!B21*(1+Underwriting!B16)^9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>Less: Vacancy &amp; Credit Loss</t>
+        </is>
+      </c>
+      <c r="C6" s="28">
+        <f>-C5*Underwriting!B12</f>
+        <v/>
+      </c>
+      <c r="D6" s="28">
+        <f>-D5*Underwriting!B12</f>
+        <v/>
+      </c>
+      <c r="E6" s="28">
+        <f>-E5*Underwriting!B12</f>
+        <v/>
+      </c>
+      <c r="F6" s="28">
+        <f>-F5*Underwriting!B12</f>
+        <v/>
+      </c>
+      <c r="G6" s="28">
+        <f>-G5*Underwriting!B12</f>
+        <v/>
+      </c>
+      <c r="H6" s="28">
+        <f>-H5*Underwriting!B12</f>
+        <v/>
+      </c>
+      <c r="I6" s="28">
+        <f>-I5*Underwriting!B12</f>
+        <v/>
+      </c>
+      <c r="J6" s="28">
+        <f>-J5*Underwriting!B12</f>
+        <v/>
+      </c>
+      <c r="K6" s="28">
+        <f>-K5*Underwriting!B12</f>
+        <v/>
+      </c>
+      <c r="L6" s="28">
+        <f>-L5*Underwriting!B12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="C7" s="28">
+        <f>Underwriting!B23*(1+Underwriting!B16)^0</f>
+        <v/>
+      </c>
+      <c r="D7" s="28">
+        <f>Underwriting!B23*(1+Underwriting!B16)^1</f>
+        <v/>
+      </c>
+      <c r="E7" s="28">
+        <f>Underwriting!B23*(1+Underwriting!B16)^2</f>
+        <v/>
+      </c>
+      <c r="F7" s="28">
+        <f>Underwriting!B23*(1+Underwriting!B16)^3</f>
+        <v/>
+      </c>
+      <c r="G7" s="28">
+        <f>Underwriting!B23*(1+Underwriting!B16)^4</f>
+        <v/>
+      </c>
+      <c r="H7" s="28">
+        <f>Underwriting!B23*(1+Underwriting!B16)^5</f>
+        <v/>
+      </c>
+      <c r="I7" s="28">
+        <f>Underwriting!B23*(1+Underwriting!B16)^6</f>
+        <v/>
+      </c>
+      <c r="J7" s="28">
+        <f>Underwriting!B23*(1+Underwriting!B16)^7</f>
+        <v/>
+      </c>
+      <c r="K7" s="28">
+        <f>Underwriting!B23*(1+Underwriting!B16)^8</f>
+        <v/>
+      </c>
+      <c r="L7" s="28">
+        <f>Underwriting!B23*(1+Underwriting!B16)^9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Effective Gross Income</t>
+        </is>
+      </c>
+      <c r="C8" s="30">
+        <f>C5+C6+C7</f>
+        <v/>
+      </c>
+      <c r="D8" s="30">
+        <f>D5+D6+D7</f>
+        <v/>
+      </c>
+      <c r="E8" s="30">
+        <f>E5+E6+E7</f>
+        <v/>
+      </c>
+      <c r="F8" s="30">
+        <f>F5+F6+F7</f>
+        <v/>
+      </c>
+      <c r="G8" s="30">
+        <f>G5+G6+G7</f>
+        <v/>
+      </c>
+      <c r="H8" s="30">
+        <f>H5+H6+H7</f>
+        <v/>
+      </c>
+      <c r="I8" s="30">
+        <f>I5+I6+I7</f>
+        <v/>
+      </c>
+      <c r="J8" s="30">
+        <f>J5+J6+J7</f>
+        <v/>
+      </c>
+      <c r="K8" s="30">
+        <f>K5+K6+K7</f>
+        <v/>
+      </c>
+      <c r="L8" s="30">
+        <f>L5+L6+L7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C9" s="28">
+        <f>Underwriting!B35*(1+Underwriting!B17)^0</f>
+        <v/>
+      </c>
+      <c r="D9" s="28">
+        <f>Underwriting!B35*(1+Underwriting!B17)^1</f>
+        <v/>
+      </c>
+      <c r="E9" s="28">
+        <f>Underwriting!B35*(1+Underwriting!B17)^2</f>
+        <v/>
+      </c>
+      <c r="F9" s="28">
+        <f>Underwriting!B35*(1+Underwriting!B17)^3</f>
+        <v/>
+      </c>
+      <c r="G9" s="28">
+        <f>Underwriting!B35*(1+Underwriting!B17)^4</f>
+        <v/>
+      </c>
+      <c r="H9" s="28">
+        <f>Underwriting!B35*(1+Underwriting!B17)^5</f>
+        <v/>
+      </c>
+      <c r="I9" s="28">
+        <f>Underwriting!B35*(1+Underwriting!B17)^6</f>
+        <v/>
+      </c>
+      <c r="J9" s="28">
+        <f>Underwriting!B35*(1+Underwriting!B17)^7</f>
+        <v/>
+      </c>
+      <c r="K9" s="28">
+        <f>Underwriting!B35*(1+Underwriting!B17)^8</f>
+        <v/>
+      </c>
+      <c r="L9" s="28">
+        <f>Underwriting!B35*(1+Underwriting!B17)^9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Net Operating Income</t>
+        </is>
+      </c>
+      <c r="C10" s="32">
+        <f>C8-C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="32">
+        <f>D8-D9</f>
+        <v/>
+      </c>
+      <c r="E10" s="32">
+        <f>E8-E9</f>
+        <v/>
+      </c>
+      <c r="F10" s="32">
+        <f>F8-F9</f>
+        <v/>
+      </c>
+      <c r="G10" s="32">
+        <f>G8-G9</f>
+        <v/>
+      </c>
+      <c r="H10" s="32">
+        <f>H8-H9</f>
+        <v/>
+      </c>
+      <c r="I10" s="32">
+        <f>I8-I9</f>
+        <v/>
+      </c>
+      <c r="J10" s="32">
+        <f>J8-J9</f>
+        <v/>
+      </c>
+      <c r="K10" s="32">
+        <f>K8-K9</f>
+        <v/>
+      </c>
+      <c r="L10" s="32">
+        <f>L8-L9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Annual Debt Service</t>
+        </is>
+      </c>
+      <c r="C11" s="28">
+        <f>IF(1&lt;=Underwriting!B49,Underwriting!B59,0)</f>
+        <v/>
+      </c>
+      <c r="D11" s="28">
+        <f>IF(2&lt;=Underwriting!B49,Underwriting!B59,0)</f>
+        <v/>
+      </c>
+      <c r="E11" s="28">
+        <f>IF(3&lt;=Underwriting!B49,Underwriting!B59,0)</f>
+        <v/>
+      </c>
+      <c r="F11" s="28">
+        <f>IF(4&lt;=Underwriting!B49,Underwriting!B59,0)</f>
+        <v/>
+      </c>
+      <c r="G11" s="28">
+        <f>IF(5&lt;=Underwriting!B49,Underwriting!B59,0)</f>
+        <v/>
+      </c>
+      <c r="H11" s="28">
+        <f>IF(6&lt;=Underwriting!B49,Underwriting!B59,0)</f>
+        <v/>
+      </c>
+      <c r="I11" s="28">
+        <f>IF(7&lt;=Underwriting!B49,Underwriting!B59,0)</f>
+        <v/>
+      </c>
+      <c r="J11" s="28">
+        <f>IF(8&lt;=Underwriting!B49,Underwriting!B59,0)</f>
+        <v/>
+      </c>
+      <c r="K11" s="28">
+        <f>IF(9&lt;=Underwriting!B49,Underwriting!B59,0)</f>
+        <v/>
+      </c>
+      <c r="L11" s="28">
+        <f>IF(10&lt;=Underwriting!B49,Underwriting!B59,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>Loan Balance (end of yr)</t>
+        </is>
+      </c>
+      <c r="B12" s="28">
+        <f>Underwriting!B54</f>
+        <v/>
+      </c>
+      <c r="C12" s="28">
+        <f>Underwriting!B54*(1+(Underwriting!B45/12))^(MIN(1,Underwriting!B46)*12)-Underwriting!B58*(((1+(Underwriting!B45/12))^(MIN(1,Underwriting!B46)*12)-1)/(Underwriting!B45/12))</f>
+        <v/>
+      </c>
+      <c r="D12" s="28">
+        <f>Underwriting!B54*(1+(Underwriting!B45/12))^(MIN(2,Underwriting!B46)*12)-Underwriting!B58*(((1+(Underwriting!B45/12))^(MIN(2,Underwriting!B46)*12)-1)/(Underwriting!B45/12))</f>
+        <v/>
+      </c>
+      <c r="E12" s="28">
+        <f>Underwriting!B54*(1+(Underwriting!B45/12))^(MIN(3,Underwriting!B46)*12)-Underwriting!B58*(((1+(Underwriting!B45/12))^(MIN(3,Underwriting!B46)*12)-1)/(Underwriting!B45/12))</f>
+        <v/>
+      </c>
+      <c r="F12" s="28">
+        <f>Underwriting!B54*(1+(Underwriting!B45/12))^(MIN(4,Underwriting!B46)*12)-Underwriting!B58*(((1+(Underwriting!B45/12))^(MIN(4,Underwriting!B46)*12)-1)/(Underwriting!B45/12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="28">
+        <f>Underwriting!B54*(1+(Underwriting!B45/12))^(MIN(5,Underwriting!B46)*12)-Underwriting!B58*(((1+(Underwriting!B45/12))^(MIN(5,Underwriting!B46)*12)-1)/(Underwriting!B45/12))</f>
+        <v/>
+      </c>
+      <c r="H12" s="28">
+        <f>Underwriting!B54*(1+(Underwriting!B45/12))^(MIN(6,Underwriting!B46)*12)-Underwriting!B58*(((1+(Underwriting!B45/12))^(MIN(6,Underwriting!B46)*12)-1)/(Underwriting!B45/12))</f>
+        <v/>
+      </c>
+      <c r="I12" s="28">
+        <f>Underwriting!B54*(1+(Underwriting!B45/12))^(MIN(7,Underwriting!B46)*12)-Underwriting!B58*(((1+(Underwriting!B45/12))^(MIN(7,Underwriting!B46)*12)-1)/(Underwriting!B45/12))</f>
+        <v/>
+      </c>
+      <c r="J12" s="28">
+        <f>Underwriting!B54*(1+(Underwriting!B45/12))^(MIN(8,Underwriting!B46)*12)-Underwriting!B58*(((1+(Underwriting!B45/12))^(MIN(8,Underwriting!B46)*12)-1)/(Underwriting!B45/12))</f>
+        <v/>
+      </c>
+      <c r="K12" s="28">
+        <f>Underwriting!B54*(1+(Underwriting!B45/12))^(MIN(9,Underwriting!B46)*12)-Underwriting!B58*(((1+(Underwriting!B45/12))^(MIN(9,Underwriting!B46)*12)-1)/(Underwriting!B45/12))</f>
+        <v/>
+      </c>
+      <c r="L12" s="28">
+        <f>Underwriting!B54*(1+(Underwriting!B45/12))^(MIN(10,Underwriting!B46)*12)-Underwriting!B58*(((1+(Underwriting!B45/12))^(MIN(10,Underwriting!B46)*12)-1)/(Underwriting!B45/12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Operating Cash Flow</t>
+        </is>
+      </c>
+      <c r="C13" s="9">
+        <f>IF(1&lt;=Underwriting!B49,C10-C11,0)</f>
+        <v/>
+      </c>
+      <c r="D13" s="9">
+        <f>IF(2&lt;=Underwriting!B49,D10-D11,0)</f>
+        <v/>
+      </c>
+      <c r="E13" s="9">
+        <f>IF(3&lt;=Underwriting!B49,E10-E11,0)</f>
+        <v/>
+      </c>
+      <c r="F13" s="9">
+        <f>IF(4&lt;=Underwriting!B49,F10-F11,0)</f>
+        <v/>
+      </c>
+      <c r="G13" s="9">
+        <f>IF(5&lt;=Underwriting!B49,G10-G11,0)</f>
+        <v/>
+      </c>
+      <c r="H13" s="9">
+        <f>IF(6&lt;=Underwriting!B49,H10-H11,0)</f>
+        <v/>
+      </c>
+      <c r="I13" s="9">
+        <f>IF(7&lt;=Underwriting!B49,I10-I11,0)</f>
+        <v/>
+      </c>
+      <c r="J13" s="9">
+        <f>IF(8&lt;=Underwriting!B49,J10-J11,0)</f>
+        <v/>
+      </c>
+      <c r="K13" s="9">
+        <f>IF(9&lt;=Underwriting!B49,K10-K11,0)</f>
+        <v/>
+      </c>
+      <c r="L13" s="9">
+        <f>IF(10&lt;=Underwriting!B49,L10-L11,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Net Sale Proceeds (reversion)</t>
+        </is>
+      </c>
+      <c r="C14" s="51">
+        <f>IF(1=Underwriting!B49,((C10*(1+Underwriting!B16))/Underwriting!B50)*(1-Underwriting!B51)-C12,0)</f>
+        <v/>
+      </c>
+      <c r="D14" s="51">
+        <f>IF(2=Underwriting!B49,((D10*(1+Underwriting!B16))/Underwriting!B50)*(1-Underwriting!B51)-D12,0)</f>
+        <v/>
+      </c>
+      <c r="E14" s="51">
+        <f>IF(3=Underwriting!B49,((E10*(1+Underwriting!B16))/Underwriting!B50)*(1-Underwriting!B51)-E12,0)</f>
+        <v/>
+      </c>
+      <c r="F14" s="51">
+        <f>IF(4=Underwriting!B49,((F10*(1+Underwriting!B16))/Underwriting!B50)*(1-Underwriting!B51)-F12,0)</f>
+        <v/>
+      </c>
+      <c r="G14" s="51">
+        <f>IF(5=Underwriting!B49,((G10*(1+Underwriting!B16))/Underwriting!B50)*(1-Underwriting!B51)-G12,0)</f>
+        <v/>
+      </c>
+      <c r="H14" s="51">
+        <f>IF(6=Underwriting!B49,((H10*(1+Underwriting!B16))/Underwriting!B50)*(1-Underwriting!B51)-H12,0)</f>
+        <v/>
+      </c>
+      <c r="I14" s="51">
+        <f>IF(7=Underwriting!B49,((I10*(1+Underwriting!B16))/Underwriting!B50)*(1-Underwriting!B51)-I12,0)</f>
+        <v/>
+      </c>
+      <c r="J14" s="51">
+        <f>IF(8=Underwriting!B49,((J10*(1+Underwriting!B16))/Underwriting!B50)*(1-Underwriting!B51)-J12,0)</f>
+        <v/>
+      </c>
+      <c r="K14" s="51">
+        <f>IF(9=Underwriting!B49,((K10*(1+Underwriting!B16))/Underwriting!B50)*(1-Underwriting!B51)-K12,0)</f>
+        <v/>
+      </c>
+      <c r="L14" s="51">
+        <f>IF(10=Underwriting!B49,((L10*(1+Underwriting!B16))/Underwriting!B50)*(1-Underwriting!B51)-L12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Total Cash Flow (for IRR)</t>
+        </is>
+      </c>
+      <c r="B15" s="32">
+        <f>-Underwriting!B57</f>
+        <v/>
+      </c>
+      <c r="C15" s="32">
+        <f>C13+C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="32">
+        <f>D13+D14</f>
+        <v/>
+      </c>
+      <c r="E15" s="32">
+        <f>E13+E14</f>
+        <v/>
+      </c>
+      <c r="F15" s="32">
+        <f>F13+F14</f>
+        <v/>
+      </c>
+      <c r="G15" s="32">
+        <f>G13+G14</f>
+        <v/>
+      </c>
+      <c r="H15" s="32">
+        <f>H13+H14</f>
+        <v/>
+      </c>
+      <c r="I15" s="32">
+        <f>I13+I14</f>
+        <v/>
+      </c>
+      <c r="J15" s="32">
+        <f>J13+J14</f>
+        <v/>
+      </c>
+      <c r="K15" s="32">
+        <f>K13+K14</f>
+        <v/>
+      </c>
+      <c r="L15" s="32">
+        <f>L13+L14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>RETURN SUMMARY (over hold period)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Levered IRR</t>
+        </is>
+      </c>
+      <c r="B18" s="33">
+        <f>IRR(B15:L15)</f>
+        <v/>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>internal rate of return on equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Equity Multiple</t>
+        </is>
+      </c>
+      <c r="B19" s="34">
+        <f>(SUM(C13:L13)+SUM(C14:L14))/-B15</f>
+        <v/>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>total cash returned / equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Avg. Cash-on-Cash</t>
+        </is>
+      </c>
+      <c r="B20" s="33">
+        <f>AVERAGEIF(C11:L11,"&gt;0",C13:L13)/Underwriting!B57</f>
+        <v/>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>avg operating CF / equity during hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Year-1 Cash-on-Cash</t>
+        </is>
+      </c>
+      <c r="B21" s="33">
+        <f>Underwriting!B64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Going-in Cap Rate</t>
+        </is>
+      </c>
+      <c r="B22" s="33">
+        <f>Underwriting!B62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Total Profit</t>
+        </is>
+      </c>
+      <c r="B23" s="32">
+        <f>SUM(C13:L13)+SUM(C14:L14)+B15</f>
+        <v/>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>all cash flows incl. equity out</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1163,28 +1871,28 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="51" t="inlineStr">
+      <c r="A5" s="52" t="inlineStr">
         <is>
           <t>Price \ Rate</t>
         </is>
       </c>
-      <c r="B5" s="52">
+      <c r="B5" s="53">
         <f>Underwriting!B45+-0.01</f>
         <v/>
       </c>
-      <c r="C5" s="52">
+      <c r="C5" s="53">
         <f>Underwriting!B45+-0.005</f>
         <v/>
       </c>
-      <c r="D5" s="52">
+      <c r="D5" s="53">
         <f>Underwriting!B45+0</f>
         <v/>
       </c>
-      <c r="E5" s="52">
+      <c r="E5" s="53">
         <f>Underwriting!B45+0.005</f>
         <v/>
       </c>
-      <c r="F5" s="52">
+      <c r="F5" s="53">
         <f>Underwriting!B45+0.01</f>
         <v/>
       </c>
@@ -1327,28 +2035,28 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="51" t="inlineStr">
+      <c r="A14" s="52" t="inlineStr">
         <is>
           <t>Price \ Rate</t>
         </is>
       </c>
-      <c r="B14" s="52">
+      <c r="B14" s="53">
         <f>Underwriting!B45+-0.01</f>
         <v/>
       </c>
-      <c r="C14" s="52">
+      <c r="C14" s="53">
         <f>Underwriting!B45+-0.005</f>
         <v/>
       </c>
-      <c r="D14" s="52">
+      <c r="D14" s="53">
         <f>Underwriting!B45+0</f>
         <v/>
       </c>
-      <c r="E14" s="52">
+      <c r="E14" s="53">
         <f>Underwriting!B45+0.005</f>
         <v/>
       </c>
-      <c r="F14" s="52">
+      <c r="F14" s="53">
         <f>Underwriting!B45+0.01</f>
         <v/>
       </c>
@@ -1358,23 +2066,23 @@
         <f>Underwriting!B9*0.9</f>
         <v/>
       </c>
-      <c r="B15" s="53">
+      <c r="B15" s="54">
         <f>Underwriting!B40/((($A15*Underwriting!B44)*(B$14/12)/(1-(1+B$14/12)^(-Underwriting!B46*12)))*12)</f>
         <v/>
       </c>
-      <c r="C15" s="53">
+      <c r="C15" s="54">
         <f>Underwriting!B40/((($A15*Underwriting!B44)*(C$14/12)/(1-(1+C$14/12)^(-Underwriting!B46*12)))*12)</f>
         <v/>
       </c>
-      <c r="D15" s="53">
+      <c r="D15" s="54">
         <f>Underwriting!B40/((($A15*Underwriting!B44)*(D$14/12)/(1-(1+D$14/12)^(-Underwriting!B46*12)))*12)</f>
         <v/>
       </c>
-      <c r="E15" s="53">
+      <c r="E15" s="54">
         <f>Underwriting!B40/((($A15*Underwriting!B44)*(E$14/12)/(1-(1+E$14/12)^(-Underwriting!B46*12)))*12)</f>
         <v/>
       </c>
-      <c r="F15" s="53">
+      <c r="F15" s="54">
         <f>Underwriting!B40/((($A15*Underwriting!B44)*(F$14/12)/(1-(1+F$14/12)^(-Underwriting!B46*12)))*12)</f>
         <v/>
       </c>
@@ -1384,23 +2092,23 @@
         <f>Underwriting!B9*0.95</f>
         <v/>
       </c>
-      <c r="B16" s="53">
+      <c r="B16" s="54">
         <f>Underwriting!B40/((($A16*Underwriting!B44)*(B$14/12)/(1-(1+B$14/12)^(-Underwriting!B46*12)))*12)</f>
         <v/>
       </c>
-      <c r="C16" s="53">
+      <c r="C16" s="54">
         <f>Underwriting!B40/((($A16*Underwriting!B44)*(C$14/12)/(1-(1+C$14/12)^(-Underwriting!B46*12)))*12)</f>
         <v/>
       </c>
-      <c r="D16" s="53">
+      <c r="D16" s="54">
         <f>Underwriting!B40/((($A16*Underwriting!B44)*(D$14/12)/(1-(1+D$14/12)^(-Underwriting!B46*12)))*12)</f>
         <v/>
       </c>
-      <c r="E16" s="53">
+      <c r="E16" s="54">
         <f>Underwriting!B40/((($A16*Underwriting!B44)*(E$14/12)/(1-(1+E$14/12)^(-Underwriting!B46*12)))*12)</f>
         <v/>
       </c>
-      <c r="F16" s="53">
+      <c r="F16" s="54">
         <f>Underwriting!B40/((($A16*Underwriting!B44)*(F$14/12)/(1-(1+F$14/12)^(-Underwriting!B46*12)))*12)</f>
         <v/>
       </c>
@@ -1410,23 +2118,23 @@
         <f>Underwriting!B9*1.0</f>
         <v/>
       </c>
-      <c r="B17" s="53">
+      <c r="B17" s="54">
         <f>Underwriting!B40/((($A17*Underwriting!B44)*(B$14/12)/(1-(1+B$14/12)^(-Underwriting!B46*12)))*12)</f>
         <v/>
       </c>
-      <c r="C17" s="53">
+      <c r="C17" s="54">
         <f>Underwriting!B40/((($A17*Underwriting!B44)*(C$14/12)/(1-(1+C$14/12)^(-Underwriting!B46*12)))*12)</f>
         <v/>
       </c>
-      <c r="D17" s="53">
+      <c r="D17" s="54">
         <f>Underwriting!B40/((($A17*Underwriting!B44)*(D$14/12)/(1-(1+D$14/12)^(-Underwriting!B46*12)))*12)</f>
         <v/>
       </c>
-      <c r="E17" s="53">
+      <c r="E17" s="54">
         <f>Underwriting!B40/((($A17*Underwriting!B44)*(E$14/12)/(1-(1+E$14/12)^(-Underwriting!B46*12)))*12)</f>
         <v/>
       </c>
-      <c r="F17" s="53">
+      <c r="F17" s="54">
         <f>Underwriting!B40/((($A17*Underwriting!B44)*(F$14/12)/(1-(1+F$14/12)^(-Underwriting!B46*12)))*12)</f>
         <v/>
       </c>
@@ -1436,23 +2144,23 @@
         <f>Underwriting!B9*1.05</f>
         <v/>
       </c>
-      <c r="B18" s="53">
+      <c r="B18" s="54">
         <f>Underwriting!B40/((($A18*Underwriting!B44)*(B$14/12)/(1-(1+B$14/12)^(-Underwriting!B46*12)))*12)</f>
         <v/>
       </c>
-      <c r="C18" s="53">
+      <c r="C18" s="54">
         <f>Underwriting!B40/((($A18*Underwriting!B44)*(C$14/12)/(1-(1+C$14/12)^(-Underwriting!B46*12)))*12)</f>
         <v/>
       </c>
-      <c r="D18" s="53">
+      <c r="D18" s="54">
         <f>Underwriting!B40/((($A18*Underwriting!B44)*(D$14/12)/(1-(1+D$14/12)^(-Underwriting!B46*12)))*12)</f>
         <v/>
       </c>
-      <c r="E18" s="53">
+      <c r="E18" s="54">
         <f>Underwriting!B40/((($A18*Underwriting!B44)*(E$14/12)/(1-(1+E$14/12)^(-Underwriting!B46*12)))*12)</f>
         <v/>
       </c>
-      <c r="F18" s="53">
+      <c r="F18" s="54">
         <f>Underwriting!B40/((($A18*Underwriting!B44)*(F$14/12)/(1-(1+F$14/12)^(-Underwriting!B46*12)))*12)</f>
         <v/>
       </c>
@@ -1462,23 +2170,23 @@
         <f>Underwriting!B9*1.1</f>
         <v/>
       </c>
-      <c r="B19" s="53">
+      <c r="B19" s="54">
         <f>Underwriting!B40/((($A19*Underwriting!B44)*(B$14/12)/(1-(1+B$14/12)^(-Underwriting!B46*12)))*12)</f>
         <v/>
       </c>
-      <c r="C19" s="53">
+      <c r="C19" s="54">
         <f>Underwriting!B40/((($A19*Underwriting!B44)*(C$14/12)/(1-(1+C$14/12)^(-Underwriting!B46*12)))*12)</f>
         <v/>
       </c>
-      <c r="D19" s="53">
+      <c r="D19" s="54">
         <f>Underwriting!B40/((($A19*Underwriting!B44)*(D$14/12)/(1-(1+D$14/12)^(-Underwriting!B46*12)))*12)</f>
         <v/>
       </c>
-      <c r="E19" s="53">
+      <c r="E19" s="54">
         <f>Underwriting!B40/((($A19*Underwriting!B44)*(E$14/12)/(1-(1+E$14/12)^(-Underwriting!B46*12)))*12)</f>
         <v/>
       </c>
-      <c r="F19" s="53">
+      <c r="F19" s="54">
         <f>Underwriting!B40/((($A19*Underwriting!B44)*(F$14/12)/(1-(1+F$14/12)^(-Underwriting!B46*12)))*12)</f>
         <v/>
       </c>
@@ -1498,24 +2206,24 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="51" t="inlineStr">
+      <c r="A24" s="52" t="inlineStr">
         <is>
           <t>Rent \ Vacancy</t>
         </is>
       </c>
-      <c r="B24" s="54" t="n">
+      <c r="B24" s="55" t="n">
         <v>0.05</v>
       </c>
-      <c r="C24" s="54" t="n">
+      <c r="C24" s="55" t="n">
         <v>0.1</v>
       </c>
-      <c r="D24" s="54" t="n">
+      <c r="D24" s="55" t="n">
         <v>0.15</v>
       </c>
-      <c r="E24" s="54" t="n">
+      <c r="E24" s="55" t="n">
         <v>0.2</v>
       </c>
-      <c r="F24" s="54" t="n">
+      <c r="F24" s="55" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -1667,7 +2375,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1771,7 +2479,7 @@
           <t>Interest Rate</t>
         </is>
       </c>
-      <c r="B11" s="44">
+      <c r="B11" s="45">
         <f>Underwriting!B45</f>
         <v/>
       </c>
@@ -1782,7 +2490,7 @@
           <t>Amortization (yrs)</t>
         </is>
       </c>
-      <c r="B12" s="48">
+      <c r="B12" s="49">
         <f>Underwriting!B46</f>
         <v/>
       </c>
@@ -1793,7 +2501,7 @@
           <t>Annual Debt Constant (per $1 loan)</t>
         </is>
       </c>
-      <c r="B13" s="40">
+      <c r="B13" s="41">
         <f>PMT(B11/12,B12*12,-1)*12</f>
         <v/>
       </c>
@@ -3825,6 +4533,347 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>OPERATOR &amp; VALUE-ADD CAPITAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>A hands-off hold: always pay a professional operator, and size the capital to finish/expand. This tab overlays the Underwriting tab so the returns reflect what you ACTUALLY pocket.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>OPERATOR  (this is a hands-off hold — always budget one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>NOI before operator</t>
+        </is>
+      </c>
+      <c r="B5" s="28">
+        <f>Underwriting!B40+Underwriting!B33</f>
+        <v/>
+      </c>
+      <c r="C5" s="15">
+        <f> Underwriting NOI + its management line (added back)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>Operator Fee ($ / month)</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>flat full-service operator; market mgmt runs ~10-12% of EGI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>Operator Fee (annual)</t>
+        </is>
+      </c>
+      <c r="B7" s="28">
+        <f>B6*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>NOI after operator</t>
+        </is>
+      </c>
+      <c r="B8" s="32">
+        <f>B5-B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>Annual Debt Service (from Underwriting)</t>
+        </is>
+      </c>
+      <c r="B9" s="28">
+        <f>Underwriting!B59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Cash Flow after operator (annual)</t>
+        </is>
+      </c>
+      <c r="B10" s="9">
+        <f>B8-B9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Cash Flow after operator (MONTHLY)</t>
+        </is>
+      </c>
+      <c r="B11" s="32">
+        <f>B10/12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Max operator you can afford ($/mo)</t>
+        </is>
+      </c>
+      <c r="B12" s="40">
+        <f>(B5-B9)/12</f>
+        <v/>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>break-even ceiling on today's income</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>DSCR after operator</t>
+        </is>
+      </c>
+      <c r="B13" s="35">
+        <f>IF(B9=0,"n/a",B8/B9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>VALUE-ADD CAPITAL  (sources &amp; uses — ON TOP of the down payment)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>Finish cabins</t>
+        </is>
+      </c>
+      <c r="B16" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>usually highest ROI — near-term income</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>Finish house / interior</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>often marginal — manager housing or defer</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Expand pads / development</t>
+        </is>
+      </c>
+      <c r="B18" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>phased — needs utilities + permits</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Infrastructure / contingency</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>septic/sewer eval, reserve</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Total Value-Add Capital</t>
+        </is>
+      </c>
+      <c r="B20" s="30">
+        <f>SUM(B16:B19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Total Cash Invested (all-in)</t>
+        </is>
+      </c>
+      <c r="B21" s="32">
+        <f>Underwriting!B57+B20</f>
+        <v/>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>down + closing + day-one capex + value-add</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>True Cash-on-Cash (today, after operator)</t>
+        </is>
+      </c>
+      <c r="B22" s="31">
+        <f>IF(B21=0,0,B10/B21)</f>
+        <v/>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>today's cash flow / all-in cash invested</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>STABILIZED  (once the build is done — enter your target NOI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>Stabilized NOI before operator</t>
+        </is>
+      </c>
+      <c r="B25" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>cabins leased, rents to market, house online</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Stabilized NOI after operator</t>
+        </is>
+      </c>
+      <c r="B26" s="9">
+        <f>IF(B25=0,0,B25-B7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>Stabilized Cash Flow (annual)</t>
+        </is>
+      </c>
+      <c r="B27" s="28">
+        <f>IF(B25=0,0,B26-B9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Stabilized Cash Flow (MONTHLY)</t>
+        </is>
+      </c>
+      <c r="B28" s="32">
+        <f>IF(B25=0,0,B27/12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Stabilized True Cash-on-Cash</t>
+        </is>
+      </c>
+      <c r="B29" s="33">
+        <f>IF(OR(B25=0,B21=0),0,B27/B21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>RULE: don't pay the seller for value YOU create with this capital (cabins, house, expansion). Require him to finish income-marketed items before close, or credit you the cost.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A15:C15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3938,7 +4987,7 @@
           <t>Annual Debt Constant k (per $1 loan)</t>
         </is>
       </c>
-      <c r="B11" s="40">
+      <c r="B11" s="41">
         <f>PMT(B8/12,B9*12,-1)*12</f>
         <v/>
       </c>
@@ -3981,12 +5030,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="41" t="inlineStr">
+      <c r="A14" s="42" t="inlineStr">
         <is>
           <t>MAXIMUM ALLOWABLE OFFER (MAO)</t>
         </is>
       </c>
-      <c r="B14" s="42">
+      <c r="B14" s="43">
         <f>MIN(B12,B13)</f>
         <v/>
       </c>
@@ -4004,27 +5053,27 @@
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="43" t="inlineStr">
+      <c r="A17" s="44" t="inlineStr">
         <is>
           <t>Lever / Metric</t>
         </is>
       </c>
-      <c r="B17" s="43" t="inlineStr">
+      <c r="B17" s="44" t="inlineStr">
         <is>
           <t>Seller Asking</t>
         </is>
       </c>
-      <c r="C17" s="43" t="inlineStr">
+      <c r="C17" s="44" t="inlineStr">
         <is>
           <t>Offer 1: Conventional</t>
         </is>
       </c>
-      <c r="D17" s="43" t="inlineStr">
+      <c r="D17" s="44" t="inlineStr">
         <is>
           <t>Offer 2: Partial Carry</t>
         </is>
       </c>
-      <c r="E17" s="43" t="inlineStr">
+      <c r="E17" s="44" t="inlineStr">
         <is>
           <t>Offer 3: Full Carry</t>
         </is>
@@ -4373,19 +5422,19 @@
           <t>Blended Rate</t>
         </is>
       </c>
-      <c r="B34" s="44">
+      <c r="B34" s="45">
         <f>IF((B29+B31)=0,0,(B29*B20+B31*B24)/(B29+B31))</f>
         <v/>
       </c>
-      <c r="C34" s="44">
+      <c r="C34" s="45">
         <f>IF((C29+C31)=0,0,(C29*C20+C31*C24)/(C29+C31))</f>
         <v/>
       </c>
-      <c r="D34" s="44">
+      <c r="D34" s="45">
         <f>IF((D29+D31)=0,0,(D29*D20+D31*D24)/(D29+D31))</f>
         <v/>
       </c>
-      <c r="E34" s="44">
+      <c r="E34" s="45">
         <f>IF((E29+E31)=0,0,(E29*E20+E31*E24)/(E29+E31))</f>
         <v/>
       </c>
@@ -4587,19 +5636,19 @@
           <t>DSCR clears target?</t>
         </is>
       </c>
-      <c r="B44" s="45">
+      <c r="B44" s="46">
         <f>IF(B33=0,"YES",IF(B39/B33&gt;=$B$5,"YES","NO"))</f>
         <v/>
       </c>
-      <c r="C44" s="45">
+      <c r="C44" s="46">
         <f>IF(C33=0,"YES",IF(C39/C33&gt;=$B$5,"YES","NO"))</f>
         <v/>
       </c>
-      <c r="D44" s="45">
+      <c r="D44" s="46">
         <f>IF(D33=0,"YES",IF(D39/D33&gt;=$B$5,"YES","NO"))</f>
         <v/>
       </c>
-      <c r="E44" s="45">
+      <c r="E44" s="46">
         <f>IF(E33=0,"YES",IF(E39/E33&gt;=$B$5,"YES","NO"))</f>
         <v/>
       </c>
@@ -4610,19 +5659,19 @@
           <t>Cash-on-Cash clears target?</t>
         </is>
       </c>
-      <c r="B45" s="45">
+      <c r="B45" s="46">
         <f>IF(B43&gt;=$B$6,"YES","NO")</f>
         <v/>
       </c>
-      <c r="C45" s="45">
+      <c r="C45" s="46">
         <f>IF(C43&gt;=$B$6,"YES","NO")</f>
         <v/>
       </c>
-      <c r="D45" s="45">
+      <c r="D45" s="46">
         <f>IF(D43&gt;=$B$6,"YES","NO")</f>
         <v/>
       </c>
-      <c r="E45" s="45">
+      <c r="E45" s="46">
         <f>IF(E43&gt;=$B$6,"YES","NO")</f>
         <v/>
       </c>
@@ -4633,19 +5682,19 @@
           <t>VERDICT</t>
         </is>
       </c>
-      <c r="B46" s="46">
+      <c r="B46" s="47">
         <f>IF(AND(B44="YES",B45="YES"),"GO",IF(OR(B44="YES",B45="YES"),"CONDITIONAL","NO-GO"))</f>
         <v/>
       </c>
-      <c r="C46" s="46">
+      <c r="C46" s="47">
         <f>IF(AND(C44="YES",C45="YES"),"GO",IF(OR(C44="YES",C45="YES"),"CONDITIONAL","NO-GO"))</f>
         <v/>
       </c>
-      <c r="D46" s="46">
+      <c r="D46" s="47">
         <f>IF(AND(D44="YES",D45="YES"),"GO",IF(OR(D44="YES",D45="YES"),"CONDITIONAL","NO-GO"))</f>
         <v/>
       </c>
-      <c r="E46" s="46">
+      <c r="E46" s="47">
         <f>IF(AND(E44="YES",E45="YES"),"GO",IF(OR(E44="YES",E45="YES"),"CONDITIONAL","NO-GO"))</f>
         <v/>
       </c>
@@ -4702,7 +5751,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4876,7 +5925,7 @@
           <t>Jan</t>
         </is>
       </c>
-      <c r="B15" s="47" t="n">
+      <c r="B15" s="48" t="n">
         <v>31</v>
       </c>
       <c r="C15" s="21" t="n">
@@ -4893,7 +5942,7 @@
           <t>Feb</t>
         </is>
       </c>
-      <c r="B16" s="47" t="n">
+      <c r="B16" s="48" t="n">
         <v>28</v>
       </c>
       <c r="C16" s="21" t="n">
@@ -4910,7 +5959,7 @@
           <t>Mar</t>
         </is>
       </c>
-      <c r="B17" s="47" t="n">
+      <c r="B17" s="48" t="n">
         <v>31</v>
       </c>
       <c r="C17" s="21" t="n">
@@ -4927,7 +5976,7 @@
           <t>Apr</t>
         </is>
       </c>
-      <c r="B18" s="47" t="n">
+      <c r="B18" s="48" t="n">
         <v>30</v>
       </c>
       <c r="C18" s="21" t="n">
@@ -4944,7 +5993,7 @@
           <t>May</t>
         </is>
       </c>
-      <c r="B19" s="47" t="n">
+      <c r="B19" s="48" t="n">
         <v>31</v>
       </c>
       <c r="C19" s="21" t="n">
@@ -4961,7 +6010,7 @@
           <t>Jun</t>
         </is>
       </c>
-      <c r="B20" s="47" t="n">
+      <c r="B20" s="48" t="n">
         <v>30</v>
       </c>
       <c r="C20" s="21" t="n">
@@ -4978,7 +6027,7 @@
           <t>Jul</t>
         </is>
       </c>
-      <c r="B21" s="47" t="n">
+      <c r="B21" s="48" t="n">
         <v>31</v>
       </c>
       <c r="C21" s="21" t="n">
@@ -4995,7 +6044,7 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="B22" s="47" t="n">
+      <c r="B22" s="48" t="n">
         <v>31</v>
       </c>
       <c r="C22" s="21" t="n">
@@ -5012,7 +6061,7 @@
           <t>Sep</t>
         </is>
       </c>
-      <c r="B23" s="47" t="n">
+      <c r="B23" s="48" t="n">
         <v>30</v>
       </c>
       <c r="C23" s="21" t="n">
@@ -5029,7 +6078,7 @@
           <t>Oct</t>
         </is>
       </c>
-      <c r="B24" s="47" t="n">
+      <c r="B24" s="48" t="n">
         <v>31</v>
       </c>
       <c r="C24" s="21" t="n">
@@ -5046,7 +6095,7 @@
           <t>Nov</t>
         </is>
       </c>
-      <c r="B25" s="47" t="n">
+      <c r="B25" s="48" t="n">
         <v>30</v>
       </c>
       <c r="C25" s="21" t="n">
@@ -5063,7 +6112,7 @@
           <t>Dec</t>
         </is>
       </c>
-      <c r="B26" s="47" t="n">
+      <c r="B26" s="48" t="n">
         <v>31</v>
       </c>
       <c r="C26" s="21" t="n">
@@ -5120,7 +6169,7 @@
           <t>Total sites in build</t>
         </is>
       </c>
-      <c r="E31" s="48">
+      <c r="E31" s="49">
         <f>B8+B11</f>
         <v/>
       </c>
@@ -5154,7 +6203,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5488,701 +6537,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>10-YEAR PRO FORMA &amp; RETURNS</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="49" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="G3" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="H3" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="I3" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="J3" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="K3" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="L3" s="16" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>Gross Potential Rent</t>
-        </is>
-      </c>
-      <c r="C5" s="28">
-        <f>Underwriting!B21*(1+Underwriting!B16)^0</f>
-        <v/>
-      </c>
-      <c r="D5" s="28">
-        <f>Underwriting!B21*(1+Underwriting!B16)^1</f>
-        <v/>
-      </c>
-      <c r="E5" s="28">
-        <f>Underwriting!B21*(1+Underwriting!B16)^2</f>
-        <v/>
-      </c>
-      <c r="F5" s="28">
-        <f>Underwriting!B21*(1+Underwriting!B16)^3</f>
-        <v/>
-      </c>
-      <c r="G5" s="28">
-        <f>Underwriting!B21*(1+Underwriting!B16)^4</f>
-        <v/>
-      </c>
-      <c r="H5" s="28">
-        <f>Underwriting!B21*(1+Underwriting!B16)^5</f>
-        <v/>
-      </c>
-      <c r="I5" s="28">
-        <f>Underwriting!B21*(1+Underwriting!B16)^6</f>
-        <v/>
-      </c>
-      <c r="J5" s="28">
-        <f>Underwriting!B21*(1+Underwriting!B16)^7</f>
-        <v/>
-      </c>
-      <c r="K5" s="28">
-        <f>Underwriting!B21*(1+Underwriting!B16)^8</f>
-        <v/>
-      </c>
-      <c r="L5" s="28">
-        <f>Underwriting!B21*(1+Underwriting!B16)^9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>Less: Vacancy &amp; Credit Loss</t>
-        </is>
-      </c>
-      <c r="C6" s="28">
-        <f>-C5*Underwriting!B12</f>
-        <v/>
-      </c>
-      <c r="D6" s="28">
-        <f>-D5*Underwriting!B12</f>
-        <v/>
-      </c>
-      <c r="E6" s="28">
-        <f>-E5*Underwriting!B12</f>
-        <v/>
-      </c>
-      <c r="F6" s="28">
-        <f>-F5*Underwriting!B12</f>
-        <v/>
-      </c>
-      <c r="G6" s="28">
-        <f>-G5*Underwriting!B12</f>
-        <v/>
-      </c>
-      <c r="H6" s="28">
-        <f>-H5*Underwriting!B12</f>
-        <v/>
-      </c>
-      <c r="I6" s="28">
-        <f>-I5*Underwriting!B12</f>
-        <v/>
-      </c>
-      <c r="J6" s="28">
-        <f>-J5*Underwriting!B12</f>
-        <v/>
-      </c>
-      <c r="K6" s="28">
-        <f>-K5*Underwriting!B12</f>
-        <v/>
-      </c>
-      <c r="L6" s="28">
-        <f>-L5*Underwriting!B12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>Other Income</t>
-        </is>
-      </c>
-      <c r="C7" s="28">
-        <f>Underwriting!B23*(1+Underwriting!B16)^0</f>
-        <v/>
-      </c>
-      <c r="D7" s="28">
-        <f>Underwriting!B23*(1+Underwriting!B16)^1</f>
-        <v/>
-      </c>
-      <c r="E7" s="28">
-        <f>Underwriting!B23*(1+Underwriting!B16)^2</f>
-        <v/>
-      </c>
-      <c r="F7" s="28">
-        <f>Underwriting!B23*(1+Underwriting!B16)^3</f>
-        <v/>
-      </c>
-      <c r="G7" s="28">
-        <f>Underwriting!B23*(1+Underwriting!B16)^4</f>
-        <v/>
-      </c>
-      <c r="H7" s="28">
-        <f>Underwriting!B23*(1+Underwriting!B16)^5</f>
-        <v/>
-      </c>
-      <c r="I7" s="28">
-        <f>Underwriting!B23*(1+Underwriting!B16)^6</f>
-        <v/>
-      </c>
-      <c r="J7" s="28">
-        <f>Underwriting!B23*(1+Underwriting!B16)^7</f>
-        <v/>
-      </c>
-      <c r="K7" s="28">
-        <f>Underwriting!B23*(1+Underwriting!B16)^8</f>
-        <v/>
-      </c>
-      <c r="L7" s="28">
-        <f>Underwriting!B23*(1+Underwriting!B16)^9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Effective Gross Income</t>
-        </is>
-      </c>
-      <c r="C8" s="30">
-        <f>C5+C6+C7</f>
-        <v/>
-      </c>
-      <c r="D8" s="30">
-        <f>D5+D6+D7</f>
-        <v/>
-      </c>
-      <c r="E8" s="30">
-        <f>E5+E6+E7</f>
-        <v/>
-      </c>
-      <c r="F8" s="30">
-        <f>F5+F6+F7</f>
-        <v/>
-      </c>
-      <c r="G8" s="30">
-        <f>G5+G6+G7</f>
-        <v/>
-      </c>
-      <c r="H8" s="30">
-        <f>H5+H6+H7</f>
-        <v/>
-      </c>
-      <c r="I8" s="30">
-        <f>I5+I6+I7</f>
-        <v/>
-      </c>
-      <c r="J8" s="30">
-        <f>J5+J6+J7</f>
-        <v/>
-      </c>
-      <c r="K8" s="30">
-        <f>K5+K6+K7</f>
-        <v/>
-      </c>
-      <c r="L8" s="30">
-        <f>L5+L6+L7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>Operating Expenses</t>
-        </is>
-      </c>
-      <c r="C9" s="28">
-        <f>Underwriting!B35*(1+Underwriting!B17)^0</f>
-        <v/>
-      </c>
-      <c r="D9" s="28">
-        <f>Underwriting!B35*(1+Underwriting!B17)^1</f>
-        <v/>
-      </c>
-      <c r="E9" s="28">
-        <f>Underwriting!B35*(1+Underwriting!B17)^2</f>
-        <v/>
-      </c>
-      <c r="F9" s="28">
-        <f>Underwriting!B35*(1+Underwriting!B17)^3</f>
-        <v/>
-      </c>
-      <c r="G9" s="28">
-        <f>Underwriting!B35*(1+Underwriting!B17)^4</f>
-        <v/>
-      </c>
-      <c r="H9" s="28">
-        <f>Underwriting!B35*(1+Underwriting!B17)^5</f>
-        <v/>
-      </c>
-      <c r="I9" s="28">
-        <f>Underwriting!B35*(1+Underwriting!B17)^6</f>
-        <v/>
-      </c>
-      <c r="J9" s="28">
-        <f>Underwriting!B35*(1+Underwriting!B17)^7</f>
-        <v/>
-      </c>
-      <c r="K9" s="28">
-        <f>Underwriting!B35*(1+Underwriting!B17)^8</f>
-        <v/>
-      </c>
-      <c r="L9" s="28">
-        <f>Underwriting!B35*(1+Underwriting!B17)^9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Net Operating Income</t>
-        </is>
-      </c>
-      <c r="C10" s="32">
-        <f>C8-C9</f>
-        <v/>
-      </c>
-      <c r="D10" s="32">
-        <f>D8-D9</f>
-        <v/>
-      </c>
-      <c r="E10" s="32">
-        <f>E8-E9</f>
-        <v/>
-      </c>
-      <c r="F10" s="32">
-        <f>F8-F9</f>
-        <v/>
-      </c>
-      <c r="G10" s="32">
-        <f>G8-G9</f>
-        <v/>
-      </c>
-      <c r="H10" s="32">
-        <f>H8-H9</f>
-        <v/>
-      </c>
-      <c r="I10" s="32">
-        <f>I8-I9</f>
-        <v/>
-      </c>
-      <c r="J10" s="32">
-        <f>J8-J9</f>
-        <v/>
-      </c>
-      <c r="K10" s="32">
-        <f>K8-K9</f>
-        <v/>
-      </c>
-      <c r="L10" s="32">
-        <f>L8-L9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>Annual Debt Service</t>
-        </is>
-      </c>
-      <c r="C11" s="28">
-        <f>IF(1&lt;=Underwriting!B49,Underwriting!B59,0)</f>
-        <v/>
-      </c>
-      <c r="D11" s="28">
-        <f>IF(2&lt;=Underwriting!B49,Underwriting!B59,0)</f>
-        <v/>
-      </c>
-      <c r="E11" s="28">
-        <f>IF(3&lt;=Underwriting!B49,Underwriting!B59,0)</f>
-        <v/>
-      </c>
-      <c r="F11" s="28">
-        <f>IF(4&lt;=Underwriting!B49,Underwriting!B59,0)</f>
-        <v/>
-      </c>
-      <c r="G11" s="28">
-        <f>IF(5&lt;=Underwriting!B49,Underwriting!B59,0)</f>
-        <v/>
-      </c>
-      <c r="H11" s="28">
-        <f>IF(6&lt;=Underwriting!B49,Underwriting!B59,0)</f>
-        <v/>
-      </c>
-      <c r="I11" s="28">
-        <f>IF(7&lt;=Underwriting!B49,Underwriting!B59,0)</f>
-        <v/>
-      </c>
-      <c r="J11" s="28">
-        <f>IF(8&lt;=Underwriting!B49,Underwriting!B59,0)</f>
-        <v/>
-      </c>
-      <c r="K11" s="28">
-        <f>IF(9&lt;=Underwriting!B49,Underwriting!B59,0)</f>
-        <v/>
-      </c>
-      <c r="L11" s="28">
-        <f>IF(10&lt;=Underwriting!B49,Underwriting!B59,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>Loan Balance (end of yr)</t>
-        </is>
-      </c>
-      <c r="B12" s="28">
-        <f>Underwriting!B54</f>
-        <v/>
-      </c>
-      <c r="C12" s="28">
-        <f>Underwriting!B54*(1+(Underwriting!B45/12))^(MIN(1,Underwriting!B46)*12)-Underwriting!B58*(((1+(Underwriting!B45/12))^(MIN(1,Underwriting!B46)*12)-1)/(Underwriting!B45/12))</f>
-        <v/>
-      </c>
-      <c r="D12" s="28">
-        <f>Underwriting!B54*(1+(Underwriting!B45/12))^(MIN(2,Underwriting!B46)*12)-Underwriting!B58*(((1+(Underwriting!B45/12))^(MIN(2,Underwriting!B46)*12)-1)/(Underwriting!B45/12))</f>
-        <v/>
-      </c>
-      <c r="E12" s="28">
-        <f>Underwriting!B54*(1+(Underwriting!B45/12))^(MIN(3,Underwriting!B46)*12)-Underwriting!B58*(((1+(Underwriting!B45/12))^(MIN(3,Underwriting!B46)*12)-1)/(Underwriting!B45/12))</f>
-        <v/>
-      </c>
-      <c r="F12" s="28">
-        <f>Underwriting!B54*(1+(Underwriting!B45/12))^(MIN(4,Underwriting!B46)*12)-Underwriting!B58*(((1+(Underwriting!B45/12))^(MIN(4,Underwriting!B46)*12)-1)/(Underwriting!B45/12))</f>
-        <v/>
-      </c>
-      <c r="G12" s="28">
-        <f>Underwriting!B54*(1+(Underwriting!B45/12))^(MIN(5,Underwriting!B46)*12)-Underwriting!B58*(((1+(Underwriting!B45/12))^(MIN(5,Underwriting!B46)*12)-1)/(Underwriting!B45/12))</f>
-        <v/>
-      </c>
-      <c r="H12" s="28">
-        <f>Underwriting!B54*(1+(Underwriting!B45/12))^(MIN(6,Underwriting!B46)*12)-Underwriting!B58*(((1+(Underwriting!B45/12))^(MIN(6,Underwriting!B46)*12)-1)/(Underwriting!B45/12))</f>
-        <v/>
-      </c>
-      <c r="I12" s="28">
-        <f>Underwriting!B54*(1+(Underwriting!B45/12))^(MIN(7,Underwriting!B46)*12)-Underwriting!B58*(((1+(Underwriting!B45/12))^(MIN(7,Underwriting!B46)*12)-1)/(Underwriting!B45/12))</f>
-        <v/>
-      </c>
-      <c r="J12" s="28">
-        <f>Underwriting!B54*(1+(Underwriting!B45/12))^(MIN(8,Underwriting!B46)*12)-Underwriting!B58*(((1+(Underwriting!B45/12))^(MIN(8,Underwriting!B46)*12)-1)/(Underwriting!B45/12))</f>
-        <v/>
-      </c>
-      <c r="K12" s="28">
-        <f>Underwriting!B54*(1+(Underwriting!B45/12))^(MIN(9,Underwriting!B46)*12)-Underwriting!B58*(((1+(Underwriting!B45/12))^(MIN(9,Underwriting!B46)*12)-1)/(Underwriting!B45/12))</f>
-        <v/>
-      </c>
-      <c r="L12" s="28">
-        <f>Underwriting!B54*(1+(Underwriting!B45/12))^(MIN(10,Underwriting!B46)*12)-Underwriting!B58*(((1+(Underwriting!B45/12))^(MIN(10,Underwriting!B46)*12)-1)/(Underwriting!B45/12))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Operating Cash Flow</t>
-        </is>
-      </c>
-      <c r="C13" s="9">
-        <f>IF(1&lt;=Underwriting!B49,C10-C11,0)</f>
-        <v/>
-      </c>
-      <c r="D13" s="9">
-        <f>IF(2&lt;=Underwriting!B49,D10-D11,0)</f>
-        <v/>
-      </c>
-      <c r="E13" s="9">
-        <f>IF(3&lt;=Underwriting!B49,E10-E11,0)</f>
-        <v/>
-      </c>
-      <c r="F13" s="9">
-        <f>IF(4&lt;=Underwriting!B49,F10-F11,0)</f>
-        <v/>
-      </c>
-      <c r="G13" s="9">
-        <f>IF(5&lt;=Underwriting!B49,G10-G11,0)</f>
-        <v/>
-      </c>
-      <c r="H13" s="9">
-        <f>IF(6&lt;=Underwriting!B49,H10-H11,0)</f>
-        <v/>
-      </c>
-      <c r="I13" s="9">
-        <f>IF(7&lt;=Underwriting!B49,I10-I11,0)</f>
-        <v/>
-      </c>
-      <c r="J13" s="9">
-        <f>IF(8&lt;=Underwriting!B49,J10-J11,0)</f>
-        <v/>
-      </c>
-      <c r="K13" s="9">
-        <f>IF(9&lt;=Underwriting!B49,K10-K11,0)</f>
-        <v/>
-      </c>
-      <c r="L13" s="9">
-        <f>IF(10&lt;=Underwriting!B49,L10-L11,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>Net Sale Proceeds (reversion)</t>
-        </is>
-      </c>
-      <c r="C14" s="50">
-        <f>IF(1=Underwriting!B49,((C10*(1+Underwriting!B16))/Underwriting!B50)*(1-Underwriting!B51)-C12,0)</f>
-        <v/>
-      </c>
-      <c r="D14" s="50">
-        <f>IF(2=Underwriting!B49,((D10*(1+Underwriting!B16))/Underwriting!B50)*(1-Underwriting!B51)-D12,0)</f>
-        <v/>
-      </c>
-      <c r="E14" s="50">
-        <f>IF(3=Underwriting!B49,((E10*(1+Underwriting!B16))/Underwriting!B50)*(1-Underwriting!B51)-E12,0)</f>
-        <v/>
-      </c>
-      <c r="F14" s="50">
-        <f>IF(4=Underwriting!B49,((F10*(1+Underwriting!B16))/Underwriting!B50)*(1-Underwriting!B51)-F12,0)</f>
-        <v/>
-      </c>
-      <c r="G14" s="50">
-        <f>IF(5=Underwriting!B49,((G10*(1+Underwriting!B16))/Underwriting!B50)*(1-Underwriting!B51)-G12,0)</f>
-        <v/>
-      </c>
-      <c r="H14" s="50">
-        <f>IF(6=Underwriting!B49,((H10*(1+Underwriting!B16))/Underwriting!B50)*(1-Underwriting!B51)-H12,0)</f>
-        <v/>
-      </c>
-      <c r="I14" s="50">
-        <f>IF(7=Underwriting!B49,((I10*(1+Underwriting!B16))/Underwriting!B50)*(1-Underwriting!B51)-I12,0)</f>
-        <v/>
-      </c>
-      <c r="J14" s="50">
-        <f>IF(8=Underwriting!B49,((J10*(1+Underwriting!B16))/Underwriting!B50)*(1-Underwriting!B51)-J12,0)</f>
-        <v/>
-      </c>
-      <c r="K14" s="50">
-        <f>IF(9=Underwriting!B49,((K10*(1+Underwriting!B16))/Underwriting!B50)*(1-Underwriting!B51)-K12,0)</f>
-        <v/>
-      </c>
-      <c r="L14" s="50">
-        <f>IF(10=Underwriting!B49,((L10*(1+Underwriting!B16))/Underwriting!B50)*(1-Underwriting!B51)-L12,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Total Cash Flow (for IRR)</t>
-        </is>
-      </c>
-      <c r="B15" s="32">
-        <f>-Underwriting!B57</f>
-        <v/>
-      </c>
-      <c r="C15" s="32">
-        <f>C13+C14</f>
-        <v/>
-      </c>
-      <c r="D15" s="32">
-        <f>D13+D14</f>
-        <v/>
-      </c>
-      <c r="E15" s="32">
-        <f>E13+E14</f>
-        <v/>
-      </c>
-      <c r="F15" s="32">
-        <f>F13+F14</f>
-        <v/>
-      </c>
-      <c r="G15" s="32">
-        <f>G13+G14</f>
-        <v/>
-      </c>
-      <c r="H15" s="32">
-        <f>H13+H14</f>
-        <v/>
-      </c>
-      <c r="I15" s="32">
-        <f>I13+I14</f>
-        <v/>
-      </c>
-      <c r="J15" s="32">
-        <f>J13+J14</f>
-        <v/>
-      </c>
-      <c r="K15" s="32">
-        <f>K13+K14</f>
-        <v/>
-      </c>
-      <c r="L15" s="32">
-        <f>L13+L14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>RETURN SUMMARY (over hold period)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Levered IRR</t>
-        </is>
-      </c>
-      <c r="B18" s="33">
-        <f>IRR(B15:L15)</f>
-        <v/>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>internal rate of return on equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Equity Multiple</t>
-        </is>
-      </c>
-      <c r="B19" s="34">
-        <f>(SUM(C13:L13)+SUM(C14:L14))/-B15</f>
-        <v/>
-      </c>
-      <c r="C19" s="15" t="inlineStr">
-        <is>
-          <t>total cash returned / equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Avg. Cash-on-Cash</t>
-        </is>
-      </c>
-      <c r="B20" s="33">
-        <f>AVERAGEIF(C11:L11,"&gt;0",C13:L13)/Underwriting!B57</f>
-        <v/>
-      </c>
-      <c r="C20" s="15" t="inlineStr">
-        <is>
-          <t>avg operating CF / equity during hold</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Year-1 Cash-on-Cash</t>
-        </is>
-      </c>
-      <c r="B21" s="33">
-        <f>Underwriting!B64</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Going-in Cap Rate</t>
-        </is>
-      </c>
-      <c r="B22" s="33">
-        <f>Underwriting!B62</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Total Profit</t>
-        </is>
-      </c>
-      <c r="B23" s="32">
-        <f>SUM(C13:L13)+SUM(C14:L14)+B15</f>
-        <v/>
-      </c>
-      <c r="C23" s="15" t="inlineStr">
-        <is>
-          <t>all cash flows incl. equity out</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A1:L1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>